--- a/Inputs/Mineral_Intensity_2025.xlsx
+++ b/Inputs/Mineral_Intensity_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Pablo\Educacion\Aprendizaje Continuo\Codigos utiles\R\Proyectos R\EV-Minerals-MONET\Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Pablo\Educacion\Aprendizaje Continuo\Codigos utiles\R\Proyectos R\ETM-Regional-Sufficiency-Circularity\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40425F67-8BB8-4E05-922A-4718BF8BD283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79578B4F-EF15-4723-8BCC-925A8722C3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3B472435-57B0-4E18-8E2C-2EA77018F632}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3B472435-57B0-4E18-8E2C-2EA77018F632}"/>
   </bookViews>
   <sheets>
     <sheet name="TD_Study_Scope" sheetId="6" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Notes" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">All_Minerals!$A$1:$F$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">All_Minerals!$A$1:$F$245</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Study_Scope!$A$1:$E$131</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="81">
   <si>
     <t>LFP</t>
   </si>
@@ -284,6 +284,12 @@
   <si>
     <t>Sum of grams_per_kWH</t>
   </si>
+  <si>
+    <t>Copper is not on the cathode, but on the negative foil material. SolidPac assumes the same thickness (1o um) as BatPac, so the mineral intensity for copper is assumed to be the same.</t>
+  </si>
+  <si>
+    <t>Copper: Cathode content (based on stochoimetry) + content  in terminals (assume results of LFP in BatPac, but using Aluminum as negative foil)</t>
+  </si>
 </sst>
 </file>
 
@@ -291,7 +297,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -352,15 +358,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,13 +376,13 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="#,##0.0"/>
+      <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="#,##0.0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -392,7 +398,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="45762.634558680555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="130" xr:uid="{7E69B710-62B6-49A5-81A2-33EA1E26ED5B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Pablo Busch" refreshedDate="45786.585957870368" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="130" xr:uid="{7E69B710-62B6-49A5-81A2-33EA1E26ED5B}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:F131" sheet="Study_Scope"/>
   </cacheSource>
@@ -467,7 +473,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC19781E-B04E-449C-B263-BC46566F7154}" name="PT_Study_Scope" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" mergeItem="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC19781E-B04E-449C-B263-BC46566F7154}" name="PT_Study_Scope" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" asteriskTotals="1" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" mergeItem="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="E7:K34" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -637,10 +643,10 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of grams_per_kWH" fld="5" baseField="0" baseItem="0" numFmtId="169"/>
+    <dataField name="Sum of grams_per_kWH" fld="5" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="2">
+    <format dxfId="3">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="0" count="0" selected="0"/>
@@ -649,7 +655,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -1003,534 +1009,534 @@
       <c r="G8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="E9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>115.4691579608788</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <v>317.59699394172191</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="8">
         <v>318.78710361072513</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="8">
         <v>849.7869319443796</v>
       </c>
     </row>
     <row r="10" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>105.71403124606368</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <v>436.14856240385365</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="8">
         <v>175.11316492903489</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="8">
         <v>851.01460815727216</v>
       </c>
     </row>
     <row r="11" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="9" t="s">
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>103.4513243478269</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>512.00883788675014</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="8">
         <v>171.30915128976429</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="8">
         <v>852.91011522195083</v>
       </c>
     </row>
     <row r="12" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="9" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>92.59201144683891</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="8">
         <v>533.9078041739474</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="8">
         <v>76.558354381027129</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="8">
         <v>853.84383685288685</v>
       </c>
     </row>
     <row r="13" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="9" t="s">
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>92.243626903558578</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>607.82224173583916</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="8">
         <v>76.262486598307348</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="8">
         <v>853.89275926723064</v>
       </c>
     </row>
     <row r="14" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="9" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>92.929939686777089</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="8">
         <v>681.36992961735291</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="8">
         <v>30.738120491197908</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="8">
         <v>853.84383685288685</v>
       </c>
     </row>
     <row r="15" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="9" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>99.365656491288505</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="8">
         <v>655.63228220156566</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="8">
         <v>123.39170410749318</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="8">
         <v>859.8047690670295</v>
       </c>
     </row>
     <row r="16" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H16" s="10">
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
         <v>88.958364763851691</v>
       </c>
-      <c r="I16" s="10">
-        <v>0</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10">
+      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8">
         <v>955.39838014713143</v>
       </c>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="9" t="s">
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>96.759076142679078</v>
       </c>
-      <c r="I17" s="10">
-        <v>0</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10">
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
         <v>805.41356940166884</v>
       </c>
     </row>
     <row r="18" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E18" s="7"/>
-      <c r="F18" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="9" t="s">
+      <c r="E18" s="10"/>
+      <c r="F18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>120.34006774721969</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="8">
         <v>332.67002970486152</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="8">
         <v>333.91662153819601</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="8">
         <v>185.85767970479458</v>
       </c>
     </row>
     <row r="19" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="9" t="s">
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>110.14939202253947</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="8">
         <v>456.96442919392473</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="8">
         <v>183.47071239923679</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="8">
         <v>186.23728998689569</v>
       </c>
     </row>
     <row r="20" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="9" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>107.79381572828821</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <v>536.52699462450562</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="8">
         <v>179.51249527747751</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="8">
         <v>186.69601800725479</v>
       </c>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="9" t="s">
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>96.428659763045857</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="8">
         <v>559.53866191362442</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="8">
         <v>80.233626168746866</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="8">
         <v>187.01213144312479</v>
       </c>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="9" t="s">
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>96.062534010121993</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="8">
         <v>636.9949186681996</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="8">
         <v>79.922735813994649</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="8">
         <v>187.01213144312479</v>
       </c>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="9" t="s">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>96.782810636510547</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="8">
         <v>714.07987616165633</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="8">
         <v>32.213739291552201</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="8">
         <v>187.01213144312479</v>
       </c>
     </row>
     <row r="24" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="9" t="s">
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>103.5687812280093</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="8">
         <v>687.43293544659514</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="8">
         <v>129.37666992165259</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="8">
         <v>188.37708194341758</v>
       </c>
     </row>
     <row r="25" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="9" t="s">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>92.989800951697234</v>
       </c>
-      <c r="I25" s="10">
-        <v>0</v>
-      </c>
-      <c r="J25" s="10">
-        <v>0</v>
-      </c>
-      <c r="K25" s="10">
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
         <v>209.79429626169477</v>
       </c>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="9" t="s">
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>100.45458443081041</v>
       </c>
-      <c r="I26" s="10">
-        <v>0</v>
-      </c>
-      <c r="J26" s="10">
-        <v>0</v>
-      </c>
-      <c r="K26" s="10">
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
         <v>175.36271920056913</v>
       </c>
     </row>
     <row r="27" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>212.85446464785841</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <v>366.22969296734885</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="8">
         <v>367.7897104020368</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="9" t="s">
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>189.92792883046516</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="8">
         <v>450.36763729801316</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="8">
         <v>180.82210775657924</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="9" t="s">
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>189.44424935966035</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="8">
         <v>552.69459085224764</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="8">
         <v>185.01629570529605</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="9" t="s">
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <v>189.4723713005925</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="8">
         <v>628.20518608072052</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="8">
         <v>90.079888107980778</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="9" t="s">
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>188.99222183031085</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="8">
         <v>715.16686629994228</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="8">
         <v>89.730845322465512</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="9" t="s">
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <v>189.93681651630288</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="8">
         <v>801.71168145281683</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="8">
         <v>36.167005898743966</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="9" t="s">
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>165.0656125169381</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="8">
         <v>663.82364337201216</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="8">
         <v>124.99712112480744</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="10">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10">
-        <v>0</v>
-      </c>
-      <c r="J34" s="10">
-        <v>0</v>
-      </c>
-      <c r="K34" s="10">
+      <c r="H34" s="8">
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="F27:F33"/>
     <mergeCell ref="E9:E26"/>
     <mergeCell ref="E27:E33"/>
     <mergeCell ref="F9:F17"/>
     <mergeCell ref="F18:F26"/>
+    <mergeCell ref="F27:F33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId2"/>
@@ -4308,7 +4314,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F37115B3-5083-4B7E-925C-5B414925D1F5}">
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -5580,162 +5586,163 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" t="s">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="F64">
-        <v>0.95539838014713141</v>
+        <f>0.161501356545118+0.372442155851388</f>
+        <v>0.53394351239650595</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" t="s">
-        <v>61</v>
+        <v>11</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F65">
-        <v>0.20979429626169477</v>
+        <v>0.38075495497149553</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="F66">
-        <v>0.80541356940166886</v>
+        <v>0.41719452082152503</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" t="s">
-        <v>62</v>
+        <v>11</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F67">
-        <v>0.17536271920056914</v>
+        <v>0.39758399321660703</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" t="s">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F68">
-        <v>0.85980476906702952</v>
+        <v>0.39400947631703143</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" t="s">
-        <v>63</v>
+        <v>11</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="F69">
-        <v>0.18837708194341757</v>
+        <v>0.37272846555500178</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="F70">
-        <v>0.8497869319443796</v>
+        <v>0.36442841755057798</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" t="s">
-        <v>64</v>
+        <v>11</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="F71">
-        <v>0.18585767970479458</v>
+        <v>0.37272846555500178</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5752,10 +5759,10 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>0.85101460815727215</v>
+        <v>0.95539838014713141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5772,10 +5779,10 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F73">
-        <v>0.18623728998689568</v>
+        <v>0.20979429626169477</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5792,10 +5799,10 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>0.85291011522195082</v>
+        <v>0.80541356940166886</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5812,10 +5819,10 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F75">
-        <v>0.1866960180072548</v>
+        <v>0.17536271920056914</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5832,10 +5839,10 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>0.85384383685288689</v>
+        <v>0.85980476906702952</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5852,10 +5859,10 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F77">
-        <v>0.18701213144312478</v>
+        <v>0.18837708194341757</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5872,10 +5879,10 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>0.85389275926723063</v>
+        <v>0.8497869319443796</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5892,10 +5899,10 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F79">
-        <v>0.18701213144312478</v>
+        <v>0.18585767970479458</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5912,10 +5919,10 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F80">
-        <v>0.85384383685288689</v>
+        <v>0.85101460815727215</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5932,330 +5939,330 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F81">
-        <v>0.18701213144312478</v>
+        <v>0.18623728998689568</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>36</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F82">
+        <v>0.85291011522195082</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>0.1866960180072548</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C84" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>22</v>
+      <c r="E84" t="s">
+        <v>20</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>0.85384383685288689</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C85" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>23</v>
+      <c r="E85" t="s">
+        <v>67</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>0.18701213144312478</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C86" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
         <v>12</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>24</v>
+      <c r="E86" t="s">
+        <v>5</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>0.85389275926723063</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>25</v>
+      <c r="E87" t="s">
+        <v>68</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>0.18701213144312478</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B88" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>26</v>
+      <c r="E88" t="s">
+        <v>21</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>0.85384383685288689</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B89" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
       </c>
-      <c r="E89" s="4" t="s">
-        <v>27</v>
+      <c r="E89" t="s">
+        <v>69</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>0.18701213144312478</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C91" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D91" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
-      </c>
-      <c r="F91" s="1">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>55</v>
-      </c>
-      <c r="E92" t="s">
-        <v>1</v>
-      </c>
-      <c r="F92" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B93" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D93" t="s">
-        <v>55</v>
-      </c>
-      <c r="E93" t="s">
-        <v>62</v>
-      </c>
-      <c r="F93" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C94" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
-      </c>
-      <c r="E94" t="s">
-        <v>2</v>
-      </c>
-      <c r="F94" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>55</v>
-      </c>
-      <c r="E95" t="s">
-        <v>63</v>
-      </c>
-      <c r="F95" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D96" t="s">
-        <v>55</v>
-      </c>
-      <c r="E96" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>55</v>
-      </c>
-      <c r="E97" t="s">
-        <v>64</v>
-      </c>
-      <c r="F97" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6272,7 +6279,7 @@
         <v>55</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F98" s="1">
         <v>1</v>
@@ -6292,7 +6299,7 @@
         <v>55</v>
       </c>
       <c r="E99" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F99" s="1">
         <v>1</v>
@@ -6312,7 +6319,7 @@
         <v>55</v>
       </c>
       <c r="E100" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -6332,7 +6339,7 @@
         <v>55</v>
       </c>
       <c r="E101" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -6352,7 +6359,7 @@
         <v>55</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -6372,7 +6379,7 @@
         <v>55</v>
       </c>
       <c r="E103" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -6392,7 +6399,7 @@
         <v>55</v>
       </c>
       <c r="E104" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -6412,7 +6419,7 @@
         <v>55</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -6432,7 +6439,7 @@
         <v>55</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F106" s="1">
         <v>1</v>
@@ -6452,7 +6459,7 @@
         <v>55</v>
       </c>
       <c r="E107" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -6463,16 +6470,16 @@
         <v>55</v>
       </c>
       <c r="B108" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D108" t="s">
         <v>55</v>
       </c>
       <c r="E108" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
@@ -6483,16 +6490,16 @@
         <v>55</v>
       </c>
       <c r="B109" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D109" t="s">
         <v>55</v>
       </c>
-      <c r="E109" s="4" t="s">
-        <v>53</v>
+      <c r="E109" t="s">
+        <v>66</v>
       </c>
       <c r="F109" s="1">
         <v>1</v>
@@ -6503,16 +6510,16 @@
         <v>55</v>
       </c>
       <c r="B110" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C110" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D110" t="s">
         <v>55</v>
       </c>
-      <c r="E110" s="4" t="s">
-        <v>22</v>
+      <c r="E110" t="s">
+        <v>20</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -6523,16 +6530,16 @@
         <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C111" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D111" t="s">
         <v>55</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>23</v>
+      <c r="E111" t="s">
+        <v>67</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -6543,16 +6550,16 @@
         <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C112" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D112" t="s">
         <v>55</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>24</v>
+      <c r="E112" t="s">
+        <v>5</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -6563,16 +6570,16 @@
         <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C113" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D113" t="s">
         <v>55</v>
       </c>
-      <c r="E113" s="4" t="s">
-        <v>25</v>
+      <c r="E113" t="s">
+        <v>68</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -6583,16 +6590,16 @@
         <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C114" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
         <v>55</v>
       </c>
-      <c r="E114" s="4" t="s">
-        <v>26</v>
+      <c r="E114" t="s">
+        <v>21</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -6603,16 +6610,16 @@
         <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C115" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D115" t="s">
         <v>55</v>
       </c>
-      <c r="E115" s="4" t="s">
-        <v>27</v>
+      <c r="E115" t="s">
+        <v>69</v>
       </c>
       <c r="F115" s="1">
         <v>1</v>
@@ -6620,162 +6627,162 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B116" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D116" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="E116" t="s">
-        <v>0</v>
-      </c>
-      <c r="F116">
-        <v>8.8958364763851688E-2</v>
+        <v>36</v>
+      </c>
+      <c r="F116" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B117" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C117" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D117" t="s">
-        <v>6</v>
-      </c>
-      <c r="E117" t="s">
-        <v>61</v>
-      </c>
-      <c r="F117">
-        <v>9.2989800951697232E-2</v>
+        <v>55</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F117" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D118" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" t="s">
+        <v>55</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F118" s="1">
         <v>1</v>
-      </c>
-      <c r="F118">
-        <v>9.6759076142679076E-2</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C119" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D119" t="s">
-        <v>6</v>
-      </c>
-      <c r="E119" t="s">
-        <v>62</v>
-      </c>
-      <c r="F119">
-        <v>0.10045458443081041</v>
+        <v>55</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F119" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C120" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D120" t="s">
-        <v>6</v>
-      </c>
-      <c r="E120" t="s">
-        <v>2</v>
-      </c>
-      <c r="F120">
-        <v>9.9365656491288507E-2</v>
+        <v>55</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F120" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B121" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C121" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D121" t="s">
-        <v>6</v>
-      </c>
-      <c r="E121" t="s">
-        <v>63</v>
-      </c>
-      <c r="F121">
-        <v>0.1035687812280093</v>
+        <v>55</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
-      </c>
-      <c r="E122" t="s">
-        <v>3</v>
-      </c>
-      <c r="F122">
-        <v>0.11546915796087881</v>
+        <v>55</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B123" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
-      </c>
-      <c r="E123" t="s">
-        <v>64</v>
-      </c>
-      <c r="F123">
-        <v>0.1203400677472197</v>
+        <v>55</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F123" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6792,10 +6799,10 @@
         <v>6</v>
       </c>
       <c r="E124" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>0.10571403124606368</v>
+        <v>8.8958364763851688E-2</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6812,10 +6819,10 @@
         <v>6</v>
       </c>
       <c r="E125" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F125">
-        <v>0.11014939202253947</v>
+        <v>9.2989800951697232E-2</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6832,10 +6839,10 @@
         <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F126">
-        <v>0.1034513243478269</v>
+        <v>9.6759076142679076E-2</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6852,10 +6859,10 @@
         <v>6</v>
       </c>
       <c r="E127" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F127">
-        <v>0.10779381572828821</v>
+        <v>0.10045458443081041</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6872,10 +6879,10 @@
         <v>6</v>
       </c>
       <c r="E128" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F128">
-        <v>9.2592011446838915E-2</v>
+        <v>9.9365656491288507E-2</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6892,10 +6899,10 @@
         <v>6</v>
       </c>
       <c r="E129" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F129">
-        <v>9.6428659763045863E-2</v>
+        <v>0.1035687812280093</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6912,10 +6919,10 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F130">
-        <v>9.2243626903558584E-2</v>
+        <v>0.11546915796087881</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6932,10 +6939,10 @@
         <v>6</v>
       </c>
       <c r="E131" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F131">
-        <v>9.6062534010121992E-2</v>
+        <v>0.1203400677472197</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6952,10 +6959,10 @@
         <v>6</v>
       </c>
       <c r="E132" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F132">
-        <v>9.2929939686777083E-2</v>
+        <v>0.10571403124606368</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6972,330 +6979,330 @@
         <v>6</v>
       </c>
       <c r="E133" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F133">
-        <v>9.6782810636510549E-2</v>
+        <v>0.11014939202253947</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B134" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C134" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D134" t="s">
         <v>6</v>
       </c>
       <c r="E134" t="s">
-        <v>36</v>
-      </c>
-      <c r="F134" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F134">
+        <v>0.1034513243478269</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C135" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D135" t="s">
         <v>6</v>
       </c>
-      <c r="E135" s="4" t="s">
-        <v>53</v>
+      <c r="E135" t="s">
+        <v>66</v>
       </c>
       <c r="F135">
-        <v>0.1650656125169381</v>
+        <v>0.10779381572828821</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B136" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D136" t="s">
         <v>6</v>
       </c>
-      <c r="E136" s="4" t="s">
-        <v>22</v>
+      <c r="E136" t="s">
+        <v>20</v>
       </c>
       <c r="F136">
-        <v>0.2128544646478584</v>
+        <v>9.2592011446838915E-2</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B137" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C137" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D137" t="s">
         <v>6</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>23</v>
+      <c r="E137" t="s">
+        <v>67</v>
       </c>
       <c r="F137">
-        <v>0.18992792883046516</v>
+        <v>9.6428659763045863E-2</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B138" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C138" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D138" t="s">
         <v>6</v>
       </c>
-      <c r="E138" s="4" t="s">
-        <v>24</v>
+      <c r="E138" t="s">
+        <v>5</v>
       </c>
       <c r="F138">
-        <v>0.18944424935966034</v>
+        <v>9.2243626903558584E-2</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C139" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D139" t="s">
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F139">
-        <v>0.1894723713005925</v>
+        <v>9.6062534010121992E-2</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C140" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D140" t="s">
         <v>6</v>
       </c>
       <c r="E140" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F140">
-        <v>0.18899222183031086</v>
+        <v>9.2929939686777083E-2</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B141" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C141" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D141" t="s">
         <v>6</v>
       </c>
       <c r="E141" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F141">
-        <v>0.18993681651630287</v>
+        <v>9.6782810636510549E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B142" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C142" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E142" t="s">
-        <v>0</v>
-      </c>
-      <c r="F142">
+        <v>36</v>
+      </c>
+      <c r="F142" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B143" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C143" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" t="s">
-        <v>61</v>
+        <v>6</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>0.1650656125169381</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B144" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C144" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="F144">
-        <v>1.2762023889936922</v>
+        <v>0.2128544646478584</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B145" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C145" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" t="s">
-        <v>62</v>
+        <v>6</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F145">
-        <v>1.3325478255353445</v>
+        <v>0.18992792883046516</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B146" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C146" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D146" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>0.18944424935966034</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B147" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C147" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E147" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>0.1894723713005925</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B148" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C148" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F148">
-        <v>0.2972028418865304</v>
+        <v>0.18899222183031086</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B149" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C149" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D149" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="F149">
-        <v>0.31130797874271998</v>
+        <v>0.18993681651630287</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -7312,10 +7319,10 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>0.24488504873242428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -7332,10 +7339,10 @@
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F151">
-        <v>0.25657256760259811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -7352,10 +7359,10 @@
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F152">
-        <v>0.15971024557711949</v>
+        <v>1.2762023889936922</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -7372,10 +7379,10 @@
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F153">
-        <v>0.16735816206591914</v>
+        <v>1.3325478255353445</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -7392,10 +7399,10 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F154">
-        <v>0.14274956693343391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -7412,10 +7419,10 @@
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F155">
-        <v>0.14960242395082141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -7432,10 +7439,10 @@
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F156">
-        <v>7.1098948136959189E-2</v>
+        <v>0.2972028418865304</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -7452,10 +7459,10 @@
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F157">
-        <v>7.4511371213658001E-2</v>
+        <v>0.31130797874271998</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -7472,10 +7479,10 @@
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F158">
-        <v>2.8656920749811864E-2</v>
+        <v>0.24488504873242428</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -7492,207 +7499,207 @@
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F159">
-        <v>3.0032629164735754E-2</v>
+        <v>0.25657256760259811</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B160" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C160" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>36</v>
-      </c>
-      <c r="F160" s="1">
-        <v>0.32200251852949441</v>
+        <v>4</v>
+      </c>
+      <c r="F160">
+        <v>0.15971024557711949</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C161" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D161" t="s">
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>0.16735816206591914</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C162" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F162">
-        <v>0.34276703074964171</v>
+        <v>0.14274956693343391</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C163" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F163">
-        <v>0.25286865603630904</v>
+        <v>0.14960242395082141</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C164" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F164">
-        <v>0.17242865834903146</v>
+        <v>7.1098948136959189E-2</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B165" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C165" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F165">
-        <v>0.16796161726293782</v>
+        <v>7.4511371213658001E-2</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B166" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C166" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F166">
-        <v>8.365539864273297E-2</v>
+        <v>2.8656920749811864E-2</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B167" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C167" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F167">
-        <v>3.371823017269631E-2</v>
+        <v>3.0032629164735754E-2</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B168" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C168" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>0</v>
-      </c>
-      <c r="F168">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0.32200251852949441</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B169" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C169" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -7700,122 +7707,122 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B170" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C170" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D170" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>0.34276703074964171</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B171" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C171" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>0.25286865603630904</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B172" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C172" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D172" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F172">
-        <v>0.65563228220156566</v>
+        <v>0.17242865834903146</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B173" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C173" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F173">
-        <v>0.68743293544659512</v>
+        <v>0.16796161726293782</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B174" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C174" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D174" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F174">
-        <v>0.31759699394172192</v>
+        <v>8.365539864273297E-2</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B175" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C175" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="F175">
-        <v>0.33267002970486154</v>
+        <v>3.371823017269631E-2</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7832,10 +7839,10 @@
         <v>7</v>
       </c>
       <c r="E176" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F176">
-        <v>0.43614856240385363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7852,10 +7859,10 @@
         <v>7</v>
       </c>
       <c r="E177" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F177">
-        <v>0.45696442919392471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7872,10 +7879,10 @@
         <v>7</v>
       </c>
       <c r="E178" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F178">
-        <v>0.51200883788675011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7892,10 +7899,10 @@
         <v>7</v>
       </c>
       <c r="E179" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F179">
-        <v>0.53652699462450559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7912,10 +7919,10 @@
         <v>7</v>
       </c>
       <c r="E180" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F180">
-        <v>0.53390780417394745</v>
+        <v>0.65563228220156566</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7932,10 +7939,10 @@
         <v>7</v>
       </c>
       <c r="E181" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F181">
-        <v>0.55953866191362445</v>
+        <v>0.68743293544659512</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7952,10 +7959,10 @@
         <v>7</v>
       </c>
       <c r="E182" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F182">
-        <v>0.60782224173583921</v>
+        <v>0.31759699394172192</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7972,10 +7979,10 @@
         <v>7</v>
       </c>
       <c r="E183" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F183">
-        <v>0.63699491866819957</v>
+        <v>0.33267002970486154</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7992,10 +7999,10 @@
         <v>7</v>
       </c>
       <c r="E184" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F184">
-        <v>0.68136992961735288</v>
+        <v>0.43614856240385363</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,190 +8019,190 @@
         <v>7</v>
       </c>
       <c r="E185" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F185">
-        <v>0.71407987616165636</v>
+        <v>0.45696442919392471</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C186" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
       </c>
       <c r="E186" t="s">
-        <v>36</v>
-      </c>
-      <c r="F186" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F186">
+        <v>0.51200883788675011</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B187" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C187" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
       </c>
       <c r="E187" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F187">
-        <v>0.66382364337201216</v>
+        <v>0.53652699462450559</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B188" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C188" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F188">
-        <v>0.36622969296734886</v>
+        <v>0.53390780417394745</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B189" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C189" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="F189">
-        <v>0.45036763729801316</v>
+        <v>0.55953866191362445</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C190" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
       </c>
       <c r="E190" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F190">
-        <v>0.55269459085224759</v>
+        <v>0.60782224173583921</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B191" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C191" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="F191">
-        <v>0.62820518608072051</v>
+        <v>0.63699491866819957</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B192" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C192" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
       </c>
       <c r="E192" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F192">
-        <v>0.71516686629994231</v>
+        <v>0.68136992961735288</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B193" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C193" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
       </c>
       <c r="E193" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F193">
-        <v>0.80171168145281679</v>
+        <v>0.71407987616165636</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B194" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C194" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D194" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E194" t="s">
-        <v>53</v>
-      </c>
-      <c r="F194">
-        <v>7.8752171663258985E-2</v>
+        <v>36</v>
+      </c>
+      <c r="F194" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -8209,13 +8216,13 @@
         <v>50</v>
       </c>
       <c r="D195" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F195">
-        <v>7.830155660747945E-2</v>
+        <v>0.66382364337201216</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -8229,13 +8236,13 @@
         <v>50</v>
       </c>
       <c r="D196" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E196" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F196">
-        <v>7.7075116651408829E-2</v>
+        <v>0.36622969296734886</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -8249,13 +8256,13 @@
         <v>50</v>
       </c>
       <c r="D197" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E197" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F197">
-        <v>7.7075116651408829E-2</v>
+        <v>0.45036763729801316</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -8269,13 +8276,13 @@
         <v>50</v>
       </c>
       <c r="D198" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F198">
-        <v>7.7075116651408829E-2</v>
+        <v>0.55269459085224759</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -8289,13 +8296,13 @@
         <v>50</v>
       </c>
       <c r="D199" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E199" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F199">
-        <v>7.7075116651408829E-2</v>
+        <v>0.62820518608072051</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -8309,193 +8316,193 @@
         <v>50</v>
       </c>
       <c r="D200" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="E200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F200">
-        <v>7.7075116651408829E-2</v>
+        <v>0.71516686629994231</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B201" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C201" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D201" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E201" t="s">
-        <v>36</v>
-      </c>
-      <c r="F201" s="1">
-        <v>0.12323990834468224</v>
+        <v>27</v>
+      </c>
+      <c r="F201">
+        <v>0.80171168145281679</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B202" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C202" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E202" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F202">
-        <v>0.40869837382957941</v>
+        <v>7.8752171663258985E-2</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B203" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C203" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D203" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E203" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F203">
-        <v>0.38480413297963395</v>
+        <v>7.830155660747945E-2</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B204" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C204" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D204" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E204" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F204">
-        <v>0.38934195671656602</v>
+        <v>7.7075116651408829E-2</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B205" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C205" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D205" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E205" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F205">
-        <v>0.36751046705644458</v>
+        <v>7.7075116651408829E-2</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B206" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C206" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D206" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E206" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F206">
-        <v>0.3401622085681742</v>
+        <v>7.7075116651408829E-2</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B207" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C207" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D207" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E207" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F207">
-        <v>0.31063572509146803</v>
+        <v>7.7075116651408829E-2</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B208" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C208" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D208" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E208" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F208">
-        <v>0.35423451029815628</v>
+        <v>7.7075116651408829E-2</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B209" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C209" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D209" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E209" t="s">
-        <v>64</v>
-      </c>
-      <c r="F209">
-        <v>0.32699555310290379</v>
+        <v>36</v>
+      </c>
+      <c r="F209" s="1">
+        <v>0.12323990834468224</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -8512,10 +8519,10 @@
         <v>18</v>
       </c>
       <c r="E210" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F210">
-        <v>0.34693450501328094</v>
+        <v>0.40869837382957941</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -8532,10 +8539,10 @@
         <v>18</v>
       </c>
       <c r="E211" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F211">
-        <v>0.31868026459441651</v>
+        <v>0.38480413297963395</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -8552,10 +8559,10 @@
         <v>18</v>
       </c>
       <c r="E212" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F212">
-        <v>0.345481413450765</v>
+        <v>0.38934195671656602</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -8572,10 +8579,10 @@
         <v>18</v>
       </c>
       <c r="E213" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F213">
-        <v>0.316958808304866</v>
+        <v>0.36751046705644458</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -8592,10 +8599,10 @@
         <v>18</v>
       </c>
       <c r="E214" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F214">
-        <v>0.33601392480656328</v>
+        <v>0.3401622085681742</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -8612,10 +8619,10 @@
         <v>18</v>
       </c>
       <c r="E215" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F215">
-        <v>0.30625426972090797</v>
+        <v>0.31063572509146803</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -8632,10 +8639,10 @@
         <v>18</v>
       </c>
       <c r="E216" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F216">
-        <v>0.3361373493952719</v>
+        <v>0.35423451029815628</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8652,10 +8659,10 @@
         <v>18</v>
       </c>
       <c r="E217" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F217">
-        <v>0.30625426972090797</v>
+        <v>0.32699555310290379</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8672,10 +8679,10 @@
         <v>18</v>
       </c>
       <c r="E218" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F218">
-        <v>0.33601392480656328</v>
+        <v>0.34693450501328094</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8692,10 +8699,10 @@
         <v>18</v>
       </c>
       <c r="E219" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F219">
-        <v>0.30625426972090797</v>
+        <v>0.31868026459441651</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8709,13 +8716,13 @@
         <v>12</v>
       </c>
       <c r="D220" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E220" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F220">
-        <v>1.0731845980866039</v>
+        <v>0.345481413450765</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8729,13 +8736,13 @@
         <v>73</v>
       </c>
       <c r="D221" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E221" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F221">
-        <v>1.0255039892283746</v>
+        <v>0.316958808304866</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8749,13 +8756,13 @@
         <v>12</v>
       </c>
       <c r="D222" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E222" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F222">
-        <v>1.0336364582553228</v>
+        <v>0.33601392480656328</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8769,13 +8776,13 @@
         <v>73</v>
       </c>
       <c r="D223" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E223" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F223">
-        <v>0.99006820331063716</v>
+        <v>0.30625426972090797</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8789,13 +8796,13 @@
         <v>12</v>
       </c>
       <c r="D224" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E224" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F224">
-        <v>0.93612708961086943</v>
+        <v>0.3361373493952719</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8809,13 +8816,13 @@
         <v>73</v>
       </c>
       <c r="D225" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E225" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F225">
-        <v>0.87793153905872956</v>
+        <v>0.30625426972090797</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8829,13 +8836,13 @@
         <v>12</v>
       </c>
       <c r="D226" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E226" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F226">
-        <v>0.96385217481856567</v>
+        <v>0.33601392480656328</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8849,13 +8856,13 @@
         <v>73</v>
       </c>
       <c r="D227" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E227" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F227">
-        <v>0.90995400952569472</v>
+        <v>0.30625426972090797</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,10 +8879,10 @@
         <v>17</v>
       </c>
       <c r="E228" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F228">
-        <v>0.94940848022468549</v>
+        <v>1.0731845980866039</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8892,10 +8899,10 @@
         <v>17</v>
       </c>
       <c r="E229" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F229">
-        <v>0.89360334351411919</v>
+        <v>1.0255039892283746</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8912,10 +8919,10 @@
         <v>17</v>
       </c>
       <c r="E230" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F230">
-        <v>0.94655005460365027</v>
+        <v>1.0336364582553228</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,10 +8939,10 @@
         <v>17</v>
       </c>
       <c r="E231" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F231">
-        <v>0.89023834779153754</v>
+        <v>0.99006820331063716</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8952,10 +8959,10 @@
         <v>17</v>
       </c>
       <c r="E232" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F232">
-        <v>0.92787452700503392</v>
+        <v>0.93612708961086943</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8972,10 +8979,10 @@
         <v>17</v>
       </c>
       <c r="E233" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F233">
-        <v>0.86921371744227882</v>
+        <v>0.87793153905872956</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8992,10 +8999,10 @@
         <v>17</v>
       </c>
       <c r="E234" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F234">
-        <v>0.9287026561694175</v>
+        <v>0.96385217481856567</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -9012,10 +9019,10 @@
         <v>17</v>
       </c>
       <c r="E235" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F235">
-        <v>0.86921371744227882</v>
+        <v>0.90995400952569472</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -9032,10 +9039,10 @@
         <v>17</v>
       </c>
       <c r="E236" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F236">
-        <v>0.92787452700503392</v>
+        <v>0.94940848022468549</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -9052,14 +9059,174 @@
         <v>17</v>
       </c>
       <c r="E237" t="s">
+        <v>65</v>
+      </c>
+      <c r="F237">
+        <v>0.89360334351411919</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>71</v>
+      </c>
+      <c r="B238" t="s">
+        <v>74</v>
+      </c>
+      <c r="C238" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" t="s">
+        <v>17</v>
+      </c>
+      <c r="E238" t="s">
+        <v>4</v>
+      </c>
+      <c r="F238">
+        <v>0.94655005460365027</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>71</v>
+      </c>
+      <c r="B239" t="s">
+        <v>74</v>
+      </c>
+      <c r="C239" t="s">
+        <v>73</v>
+      </c>
+      <c r="D239" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239" t="s">
+        <v>66</v>
+      </c>
+      <c r="F239">
+        <v>0.89023834779153754</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>71</v>
+      </c>
+      <c r="B240" t="s">
+        <v>74</v>
+      </c>
+      <c r="C240" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240" t="s">
+        <v>20</v>
+      </c>
+      <c r="F240">
+        <v>0.92787452700503392</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>71</v>
+      </c>
+      <c r="B241" t="s">
+        <v>74</v>
+      </c>
+      <c r="C241" t="s">
+        <v>73</v>
+      </c>
+      <c r="D241" t="s">
+        <v>17</v>
+      </c>
+      <c r="E241" t="s">
+        <v>67</v>
+      </c>
+      <c r="F241">
+        <v>0.86921371744227882</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>71</v>
+      </c>
+      <c r="B242" t="s">
+        <v>74</v>
+      </c>
+      <c r="C242" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
+        <v>17</v>
+      </c>
+      <c r="E242" t="s">
+        <v>5</v>
+      </c>
+      <c r="F242">
+        <v>0.9287026561694175</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>71</v>
+      </c>
+      <c r="B243" t="s">
+        <v>74</v>
+      </c>
+      <c r="C243" t="s">
+        <v>73</v>
+      </c>
+      <c r="D243" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243" t="s">
+        <v>68</v>
+      </c>
+      <c r="F243">
+        <v>0.86921371744227882</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>71</v>
+      </c>
+      <c r="B244" t="s">
+        <v>74</v>
+      </c>
+      <c r="C244" t="s">
+        <v>12</v>
+      </c>
+      <c r="D244" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244" t="s">
+        <v>21</v>
+      </c>
+      <c r="F244">
+        <v>0.92787452700503392</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>71</v>
+      </c>
+      <c r="B245" t="s">
+        <v>74</v>
+      </c>
+      <c r="C245" t="s">
+        <v>73</v>
+      </c>
+      <c r="D245" t="s">
+        <v>17</v>
+      </c>
+      <c r="E245" t="s">
         <v>69</v>
       </c>
-      <c r="F237">
+      <c r="F245">
         <v>0.86921371744227882</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F237" xr:uid="{F37115B3-5083-4B7E-925C-5B414925D1F5}"/>
+  <autoFilter ref="A1:F245" xr:uid="{F37115B3-5083-4B7E-925C-5B414925D1F5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
@@ -9067,7 +9234,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF9921A-2AF2-427D-BDE8-40DF7EC99149}">
-  <dimension ref="B1:E26"/>
+  <dimension ref="B1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.140625" customWidth="1"/>
@@ -9174,56 +9341,66 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
         <v>54</v>
       </c>
     </row>
